--- a/dados/inscricoes.xlsx
+++ b/dados/inscricoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://risctechnology-my.sharepoint.com/personal/rafael_nicolucci_risctech_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_0454189C3E0185D6688521B2BD84F09C166E8B8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{593EBA27-1668-4C01-9E60-F3FA52305343}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_0454189C387187B8573D2C9DCF752FA57265BE47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0660D1BD-2F4D-4198-84B5-2309A366E026}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Respostas ao formulário 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Respostas ao formulário 1'!$A$1:$I$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Respostas ao formulário 1'!$A$1:$I$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -83,7 +83,7 @@
     <t>IPB - Itu</t>
   </si>
   <si>
-    <t>À VISTA - Valor R$ 200,00</t>
+    <t>ACAMPAMENTO COMPLETO – PIX – R$ 200,00</t>
   </si>
   <si>
     <t xml:space="preserve">João Guilherme Ferreira Silva </t>
@@ -188,9 +188,6 @@
     <t xml:space="preserve">Davi Ricardo Rodrigues Campos </t>
   </si>
   <si>
-    <t>ACAMPAMENTO COMPLETO – PIX – R$ 200,00</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wellington Mendes de Queiroz </t>
   </si>
   <si>
@@ -306,6 +303,9 @@
   </si>
   <si>
     <t>Intolerância a lactose</t>
+  </si>
+  <si>
+    <t>Eric Tiago Machado Vieira</t>
   </si>
   <si>
     <t>Daniele Lopes Ferreira - não inscrito Pago dia 25/02</t>
@@ -343,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -366,6 +366,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -419,15 +425,33 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -452,29 +476,13 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respostas ao formulário 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -489,8 +497,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:I62">
-  <autoFilter ref="A1:I62" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:I63">
+  <autoFilter ref="A1:I63" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Carimbo de data/hora"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome completo"/>
@@ -707,10 +715,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="35.42578125" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" customWidth="1"/>
@@ -1520,7 +1528,7 @@
       <c r="F27" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="5">
@@ -1550,7 +1558,7 @@
       <c r="F28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="5">
@@ -1580,7 +1588,7 @@
       <c r="F29" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="5">
@@ -1610,7 +1618,7 @@
       <c r="F30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H30" s="5">
@@ -1671,7 +1679,7 @@
         <v>11</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H32" s="11">
         <v>200</v>
@@ -1686,7 +1694,7 @@
         <v>46074.953141365739</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33" s="10">
         <v>33</v>
@@ -1698,10 +1706,10 @@
         <v>10</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H33" s="11">
         <v>200</v>
@@ -1716,7 +1724,7 @@
         <v>46075.539279652774</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="4">
         <v>12</v>
@@ -1728,10 +1736,10 @@
         <v>10</v>
       </c>
       <c r="F34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="H34" s="5">
         <v>0</v>
@@ -1746,7 +1754,7 @@
         <v>46075.750952465278</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C35" s="10">
         <v>23</v>
@@ -1758,10 +1766,10 @@
         <v>45</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H35" s="11">
         <v>200</v>
@@ -1776,7 +1784,7 @@
         <v>46075.753208020833</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" s="10">
         <v>20</v>
@@ -1788,10 +1796,10 @@
         <v>45</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H36" s="11">
         <v>200</v>
@@ -1806,7 +1814,7 @@
         <v>46078.293629756939</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" s="10">
         <v>34</v>
@@ -1818,10 +1826,10 @@
         <v>25</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H37" s="11">
         <v>200</v>
@@ -1836,7 +1844,7 @@
         <v>46078.953542696763</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C38" s="4">
         <v>36</v>
@@ -1848,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H38" s="5">
         <v>0</v>
@@ -1866,7 +1874,7 @@
         <v>46078.956307638888</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C39" s="4">
         <v>38</v>
@@ -1881,7 +1889,7 @@
         <v>11</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H39" s="5">
         <v>0</v>
@@ -1896,7 +1904,7 @@
         <v>46079.451820046292</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C40" s="4">
         <v>30</v>
@@ -1908,10 +1916,10 @@
         <v>10</v>
       </c>
       <c r="F40" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="H40" s="5">
         <v>0</v>
@@ -1925,7 +1933,7 @@
         <v>46079.453458807868</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C41" s="4">
         <v>34</v>
@@ -1937,10 +1945,10 @@
         <v>10</v>
       </c>
       <c r="F41" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="H41" s="5">
         <v>0</v>
@@ -1954,7 +1962,7 @@
         <v>46082.545930879627</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C42" s="4">
         <v>34</v>
@@ -1966,10 +1974,10 @@
         <v>10</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H42" s="5">
         <v>0</v>
@@ -1983,7 +1991,7 @@
         <v>46082.546974305558</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C43" s="4">
         <v>37</v>
@@ -1995,10 +2003,10 @@
         <v>10</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H43" s="5">
         <v>0</v>
@@ -2012,7 +2020,7 @@
         <v>46082.826216666668</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C44" s="4">
         <v>10</v>
@@ -2024,10 +2032,10 @@
         <v>10</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H44" s="5">
         <v>0</v>
@@ -2041,7 +2049,7 @@
         <v>46082.826855636573</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C45" s="4">
         <v>7</v>
@@ -2053,10 +2061,10 @@
         <v>10</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H45" s="5">
         <v>0</v>
@@ -2070,7 +2078,7 @@
         <v>46082.866330081015</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C46" s="4">
         <v>19</v>
@@ -2082,16 +2090,16 @@
         <v>14</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H46" s="5">
         <v>0</v>
       </c>
       <c r="I46" s="5">
-        <f t="shared" ref="I46:I62" si="2">200-H46</f>
+        <f t="shared" ref="I46:I63" si="2">200-H46</f>
         <v>200</v>
       </c>
     </row>
@@ -2100,7 +2108,7 @@
         <v>46083.51295694444</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C47" s="10">
         <v>19</v>
@@ -2112,10 +2120,10 @@
         <v>14</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H47" s="11">
         <v>200</v>
@@ -2130,7 +2138,7 @@
         <v>46084.474167118053</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C48" s="7">
         <v>12</v>
@@ -2139,13 +2147,13 @@
         <v>15981381818</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H48" s="8">
         <v>150</v>
@@ -2160,7 +2168,7 @@
         <v>46088.447956319447</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" s="10">
         <v>61</v>
@@ -2172,10 +2180,10 @@
         <v>40</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H49" s="11">
         <v>200</v>
@@ -2190,7 +2198,7 @@
         <v>46088.449011053242</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C50" s="10">
         <v>64</v>
@@ -2202,10 +2210,10 @@
         <v>40</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H50" s="11">
         <v>200</v>
@@ -2220,7 +2228,7 @@
         <v>46091.45505960648</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C51" s="4">
         <v>37</v>
@@ -2235,7 +2243,7 @@
         <v>11</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H51" s="5">
         <v>0</v>
@@ -2250,7 +2258,7 @@
         <v>46091.457525555554</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C52" s="4">
         <v>30</v>
@@ -2265,7 +2273,7 @@
         <v>11</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H52" s="5">
         <v>0</v>
@@ -2280,7 +2288,7 @@
         <v>46091.902087141207</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C53" s="4">
         <v>23</v>
@@ -2292,10 +2300,10 @@
         <v>45</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H53" s="5">
         <v>0</v>
@@ -2310,7 +2318,7 @@
         <v>46093.270185775458</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C54" s="10">
         <v>58</v>
@@ -2322,10 +2330,10 @@
         <v>40</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H54" s="11">
         <v>200</v>
@@ -2340,7 +2348,7 @@
         <v>46093.27149944444</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C55" s="10">
         <v>58</v>
@@ -2352,10 +2360,10 @@
         <v>40</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H55" s="11">
         <v>200</v>
@@ -2370,7 +2378,7 @@
         <v>46093.422185185183</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C56" s="4">
         <v>35</v>
@@ -2382,10 +2390,10 @@
         <v>10</v>
       </c>
       <c r="F56" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="H56" s="5">
         <v>0</v>
@@ -2400,7 +2408,7 @@
         <v>46093.422877638892</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C57" s="4">
         <v>40</v>
@@ -2412,10 +2420,10 @@
         <v>10</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H57" s="5">
         <v>0</v>
@@ -2430,7 +2438,7 @@
         <v>46093.423782372687</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C58" s="4">
         <v>9</v>
@@ -2442,10 +2450,10 @@
         <v>10</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H58" s="5">
         <v>0</v>
@@ -2460,7 +2468,7 @@
         <v>46093.424697407405</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59" s="4">
         <v>5</v>
@@ -2472,10 +2480,10 @@
         <v>10</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H59" s="5">
         <v>0</v>
@@ -2490,7 +2498,7 @@
         <v>46093.523896493054</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C60" s="4">
         <v>27</v>
@@ -2502,10 +2510,10 @@
         <v>10</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H60" s="5">
         <v>0</v>
@@ -2520,7 +2528,7 @@
         <v>46093.708566168978</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C61" s="10">
         <v>19</v>
@@ -2532,10 +2540,10 @@
         <v>14</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H61" s="11">
         <v>200</v>
@@ -2550,7 +2558,7 @@
         <v>46094.710265729169</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C62" s="4">
         <v>19</v>
@@ -2559,13 +2567,13 @@
         <v>11955200793</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F62" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F62" s="12" t="s">
-        <v>89</v>
-      </c>
       <c r="G62" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H62" s="5">
         <v>0</v>
@@ -2575,437 +2583,427 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
+    <row r="63" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
+        <v>46095.346177013889</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="4">
+        <v>37</v>
+      </c>
+      <c r="D63" s="4">
+        <v>15997232525</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H63" s="5">
+        <v>0</v>
+      </c>
+      <c r="I63" s="5">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="64" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-    </row>
-    <row r="65" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A65" s="14"/>
-      <c r="B65" s="14" t="s">
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+    </row>
+    <row r="65" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+    </row>
+    <row r="66" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A66" s="15"/>
+      <c r="B66" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="15">
-        <v>200</v>
-      </c>
-      <c r="I65" s="15">
-        <f t="shared" ref="I65:I66" si="3">200-H65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14" t="s">
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="16">
+        <v>200</v>
+      </c>
+      <c r="I66" s="16">
+        <f t="shared" ref="I66:I67" si="3">200-H66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A67" s="15"/>
+      <c r="B67" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="15">
-        <v>200</v>
-      </c>
-      <c r="I66" s="15">
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="15"/>
+      <c r="G67" s="15"/>
+      <c r="H67" s="16">
+        <v>200</v>
+      </c>
+      <c r="I67" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-    </row>
-    <row r="68" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="G68" s="16"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="16"/>
-    </row>
-    <row r="69" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-    </row>
-    <row r="70" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="G70" s="16"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-    </row>
-    <row r="71" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-    </row>
-    <row r="72" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-    </row>
-    <row r="73" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="G73" s="16"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-    </row>
-    <row r="74" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-    </row>
-    <row r="75" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-    </row>
-    <row r="76" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-    </row>
-    <row r="77" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-    </row>
-    <row r="78" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-    </row>
-    <row r="79" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-    </row>
-    <row r="80" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
+    <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+    </row>
+    <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+    </row>
+    <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+    </row>
+    <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+    </row>
+    <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+    </row>
+    <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+    </row>
+    <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+    </row>
+    <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+    </row>
+    <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+    </row>
+    <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+    </row>
+    <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+    </row>
+    <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+    </row>
+    <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
     </row>
     <row r="81" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
     </row>
     <row r="82" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
     </row>
     <row r="83" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
     </row>
     <row r="84" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
     </row>
     <row r="85" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
     </row>
     <row r="86" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
     </row>
     <row r="87" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
     </row>
     <row r="88" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H88" s="13"/>
-      <c r="I88" s="13"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
     </row>
     <row r="89" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
     </row>
     <row r="90" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
     </row>
     <row r="91" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
     </row>
     <row r="92" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H92" s="13"/>
-      <c r="I92" s="13"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
     </row>
     <row r="93" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
     </row>
     <row r="94" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
     </row>
     <row r="95" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H95" s="13"/>
-      <c r="I95" s="13"/>
+      <c r="H95" s="14"/>
+      <c r="I95" s="14"/>
     </row>
     <row r="96" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
     </row>
     <row r="97" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H97" s="13"/>
-      <c r="I97" s="13"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
     </row>
     <row r="98" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
+      <c r="H98" s="14"/>
+      <c r="I98" s="14"/>
     </row>
     <row r="99" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H99" s="13"/>
-      <c r="I99" s="13"/>
+      <c r="H99" s="14"/>
+      <c r="I99" s="14"/>
     </row>
     <row r="100" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
+      <c r="H100" s="14"/>
+      <c r="I100" s="14"/>
     </row>
     <row r="101" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
     </row>
     <row r="102" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14"/>
     </row>
     <row r="103" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H103" s="13"/>
-      <c r="I103" s="13"/>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
     </row>
     <row r="104" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H104" s="13"/>
-      <c r="I104" s="13"/>
+      <c r="H104" s="14"/>
+      <c r="I104" s="14"/>
     </row>
     <row r="105" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H105" s="13"/>
-      <c r="I105" s="13"/>
+      <c r="H105" s="14"/>
+      <c r="I105" s="14"/>
     </row>
     <row r="106" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H106" s="13"/>
-      <c r="I106" s="13"/>
+      <c r="H106" s="14"/>
+      <c r="I106" s="14"/>
     </row>
     <row r="107" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H107" s="13"/>
-      <c r="I107" s="13"/>
+      <c r="H107" s="14"/>
+      <c r="I107" s="14"/>
     </row>
     <row r="108" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H108" s="13"/>
-      <c r="I108" s="13"/>
+      <c r="H108" s="14"/>
+      <c r="I108" s="14"/>
     </row>
     <row r="109" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H109" s="13"/>
-      <c r="I109" s="13"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="14"/>
     </row>
     <row r="110" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H110" s="13"/>
-      <c r="I110" s="13"/>
+      <c r="H110" s="14"/>
+      <c r="I110" s="14"/>
     </row>
     <row r="111" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H111" s="13"/>
-      <c r="I111" s="13"/>
+      <c r="H111" s="14"/>
+      <c r="I111" s="14"/>
     </row>
     <row r="112" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H112" s="13"/>
-      <c r="I112" s="13"/>
+      <c r="H112" s="14"/>
+      <c r="I112" s="14"/>
     </row>
     <row r="113" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H113" s="13"/>
-      <c r="I113" s="13"/>
+      <c r="H113" s="14"/>
+      <c r="I113" s="14"/>
     </row>
     <row r="114" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H114" s="13"/>
-      <c r="I114" s="13"/>
+      <c r="H114" s="14"/>
+      <c r="I114" s="14"/>
     </row>
     <row r="115" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H115" s="13"/>
-      <c r="I115" s="13"/>
+      <c r="H115" s="14"/>
+      <c r="I115" s="14"/>
     </row>
     <row r="116" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H116" s="13"/>
-      <c r="I116" s="13"/>
+      <c r="H116" s="14"/>
+      <c r="I116" s="14"/>
     </row>
     <row r="117" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H117" s="13"/>
-      <c r="I117" s="13"/>
+      <c r="H117" s="14"/>
+      <c r="I117" s="14"/>
     </row>
     <row r="118" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H118" s="13"/>
-      <c r="I118" s="13"/>
+      <c r="H118" s="14"/>
+      <c r="I118" s="14"/>
     </row>
     <row r="119" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H119" s="13"/>
-      <c r="I119" s="13"/>
+      <c r="H119" s="14"/>
+      <c r="I119" s="14"/>
     </row>
     <row r="120" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H120" s="13"/>
-      <c r="I120" s="13"/>
+      <c r="H120" s="14"/>
+      <c r="I120" s="14"/>
     </row>
     <row r="121" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H121" s="13"/>
-      <c r="I121" s="13"/>
+      <c r="H121" s="14"/>
+      <c r="I121" s="14"/>
     </row>
     <row r="122" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H122" s="13"/>
-      <c r="I122" s="13"/>
+      <c r="H122" s="14"/>
+      <c r="I122" s="14"/>
     </row>
     <row r="123" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H123" s="13"/>
-      <c r="I123" s="13"/>
+      <c r="H123" s="14"/>
+      <c r="I123" s="14"/>
     </row>
     <row r="124" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H124" s="13"/>
-      <c r="I124" s="13"/>
+      <c r="H124" s="14"/>
+      <c r="I124" s="14"/>
     </row>
     <row r="125" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H125" s="13"/>
-      <c r="I125" s="13"/>
+      <c r="H125" s="14"/>
+      <c r="I125" s="14"/>
     </row>
     <row r="126" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H126" s="13"/>
-      <c r="I126" s="13"/>
+      <c r="H126" s="14"/>
+      <c r="I126" s="14"/>
     </row>
     <row r="127" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H127" s="13"/>
-      <c r="I127" s="13"/>
+      <c r="H127" s="14"/>
+      <c r="I127" s="14"/>
     </row>
     <row r="128" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H128" s="13"/>
-      <c r="I128" s="13"/>
+      <c r="H128" s="14"/>
+      <c r="I128" s="14"/>
     </row>
     <row r="129" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H129" s="13"/>
-      <c r="I129" s="13"/>
+      <c r="H129" s="14"/>
+      <c r="I129" s="14"/>
     </row>
     <row r="130" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H130" s="13"/>
-      <c r="I130" s="13"/>
+      <c r="H130" s="14"/>
+      <c r="I130" s="14"/>
     </row>
     <row r="131" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H131" s="13"/>
-      <c r="I131" s="13"/>
+      <c r="H131" s="14"/>
+      <c r="I131" s="14"/>
     </row>
     <row r="132" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H132" s="13"/>
-      <c r="I132" s="13"/>
+      <c r="H132" s="14"/>
+      <c r="I132" s="14"/>
     </row>
     <row r="133" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H133" s="13"/>
-      <c r="I133" s="13"/>
+      <c r="H133" s="14"/>
+      <c r="I133" s="14"/>
     </row>
     <row r="134" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H134" s="13"/>
-      <c r="I134" s="13"/>
+      <c r="H134" s="14"/>
+      <c r="I134" s="14"/>
     </row>
     <row r="135" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H135" s="13"/>
-      <c r="I135" s="13"/>
+      <c r="H135" s="14"/>
+      <c r="I135" s="14"/>
     </row>
     <row r="136" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H136" s="13"/>
-      <c r="I136" s="13"/>
+      <c r="H136" s="14"/>
+      <c r="I136" s="14"/>
     </row>
     <row r="137" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H137" s="13"/>
-      <c r="I137" s="13"/>
+      <c r="H137" s="14"/>
+      <c r="I137" s="14"/>
     </row>
     <row r="138" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H138" s="13"/>
-      <c r="I138" s="13"/>
+      <c r="H138" s="14"/>
+      <c r="I138" s="14"/>
     </row>
     <row r="139" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H139" s="13"/>
-      <c r="I139" s="13"/>
+      <c r="H139" s="14"/>
+      <c r="I139" s="14"/>
     </row>
     <row r="140" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H140" s="13"/>
-      <c r="I140" s="13"/>
+      <c r="H140" s="14"/>
+      <c r="I140" s="14"/>
     </row>
     <row r="141" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H141" s="13"/>
-      <c r="I141" s="13"/>
+      <c r="H141" s="14"/>
+      <c r="I141" s="14"/>
     </row>
     <row r="142" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H142" s="13"/>
-      <c r="I142" s="13"/>
+      <c r="H142" s="14"/>
+      <c r="I142" s="14"/>
     </row>
     <row r="143" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H143" s="13"/>
-      <c r="I143" s="13"/>
+      <c r="H143" s="14"/>
+      <c r="I143" s="14"/>
     </row>
     <row r="144" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H144" s="13"/>
-      <c r="I144" s="13"/>
+      <c r="H144" s="14"/>
+      <c r="I144" s="14"/>
     </row>
     <row r="145" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H145" s="13"/>
-      <c r="I145" s="13"/>
+      <c r="H145" s="14"/>
+      <c r="I145" s="14"/>
     </row>
     <row r="146" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H146" s="13"/>
-      <c r="I146" s="13"/>
+      <c r="H146" s="14"/>
+      <c r="I146" s="14"/>
     </row>
     <row r="147" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H147" s="13"/>
-      <c r="I147" s="13"/>
+      <c r="H147" s="14"/>
+      <c r="I147" s="14"/>
     </row>
     <row r="148" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H148" s="13"/>
-      <c r="I148" s="13"/>
+      <c r="H148" s="14"/>
+      <c r="I148" s="14"/>
     </row>
     <row r="149" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H149" s="13"/>
-      <c r="I149" s="13"/>
+      <c r="H149" s="14"/>
+      <c r="I149" s="14"/>
     </row>
     <row r="150" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H150" s="13"/>
-      <c r="I150" s="13"/>
+      <c r="H150" s="14"/>
+      <c r="I150" s="14"/>
     </row>
     <row r="151" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H151" s="13"/>
-      <c r="I151" s="13"/>
+      <c r="H151" s="14"/>
+      <c r="I151" s="14"/>
     </row>
     <row r="152" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H152" s="13"/>
-      <c r="I152" s="13"/>
+      <c r="H152" s="14"/>
+      <c r="I152" s="14"/>
     </row>
     <row r="153" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H153" s="13"/>
-      <c r="I153" s="13"/>
+      <c r="H153" s="14"/>
+      <c r="I153" s="14"/>
     </row>
     <row r="154" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H154" s="13"/>
-      <c r="I154" s="13"/>
-    </row>
-    <row r="155" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H155" s="13"/>
-      <c r="I155" s="13"/>
-    </row>
-    <row r="156" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H156" s="13"/>
-      <c r="I156" s="13"/>
-    </row>
-    <row r="157" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H157" s="13"/>
-      <c r="I157" s="13"/>
-    </row>
-    <row r="158" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H158" s="13"/>
-      <c r="I158" s="13"/>
-    </row>
-    <row r="159" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H159" s="13"/>
-      <c r="I159" s="13"/>
-    </row>
-    <row r="160" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H160" s="13"/>
-      <c r="I160" s="13"/>
-    </row>
-    <row r="161" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H161" s="13"/>
-      <c r="I161" s="13"/>
-    </row>
-    <row r="162" spans="8:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H162" s="13"/>
-      <c r="I162" s="13"/>
+      <c r="H154" s="14"/>
+      <c r="I154" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/inscricoes.xlsx
+++ b/dados/inscricoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://risctechnology-my.sharepoint.com/personal/rafael_nicolucci_risctech_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_0454189C387187B8573D2C9DCF752FA57265BE47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0660D1BD-2F4D-4198-84B5-2309A366E026}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_0454189C387187B8573D2C9DCF752FA57265BE47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8F8FB3A-44D9-404C-9F6E-DD12CFF8CCE6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="91">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -249,9 +249,6 @@
   </si>
   <si>
     <t>Análise Souto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">São Miguel Arcanjo </t>
   </si>
   <si>
     <t xml:space="preserve">Fátima da Silva </t>
@@ -437,22 +434,6 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
@@ -476,13 +457,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respostas ao formulário 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -494,6 +491,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2147,7 +2148,7 @@
         <v>15981381818</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>51</v>
@@ -2168,7 +2169,7 @@
         <v>46088.447956319447</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C49" s="10">
         <v>61</v>
@@ -2198,7 +2199,7 @@
         <v>46088.449011053242</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C50" s="10">
         <v>64</v>
@@ -2228,7 +2229,7 @@
         <v>46091.45505960648</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C51" s="4">
         <v>37</v>
@@ -2258,7 +2259,7 @@
         <v>46091.457525555554</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C52" s="4">
         <v>30</v>
@@ -2288,7 +2289,7 @@
         <v>46091.902087141207</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C53" s="4">
         <v>23</v>
@@ -2300,7 +2301,7 @@
         <v>45</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>15</v>
@@ -2318,7 +2319,7 @@
         <v>46093.270185775458</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C54" s="10">
         <v>58</v>
@@ -2348,7 +2349,7 @@
         <v>46093.27149944444</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C55" s="10">
         <v>58</v>
@@ -2378,7 +2379,7 @@
         <v>46093.422185185183</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C56" s="4">
         <v>35</v>
@@ -2408,7 +2409,7 @@
         <v>46093.422877638892</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C57" s="4">
         <v>40</v>
@@ -2438,7 +2439,7 @@
         <v>46093.423782372687</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C58" s="4">
         <v>9</v>
@@ -2468,7 +2469,7 @@
         <v>46093.424697407405</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C59" s="4">
         <v>5</v>
@@ -2498,7 +2499,7 @@
         <v>46093.523896493054</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C60" s="4">
         <v>27</v>
@@ -2528,7 +2529,7 @@
         <v>46093.708566168978</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C61" s="10">
         <v>19</v>
@@ -2558,7 +2559,7 @@
         <v>46094.710265729169</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C62" s="4">
         <v>19</v>
@@ -2567,10 +2568,10 @@
         <v>11955200793</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F62" s="12" t="s">
         <v>87</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>88</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>54</v>
@@ -2588,7 +2589,7 @@
         <v>46095.346177013889</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C63" s="4">
         <v>37</v>
@@ -2624,7 +2625,7 @@
     <row r="66" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="15"/>
       <c r="B66" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15"/>
@@ -2642,7 +2643,7 @@
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="15"/>
       <c r="B67" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C67" s="15"/>
       <c r="D67" s="15"/>
